--- a/data/trans_dic/POLIPATOLOGIA_Lim_2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/POLIPATOLOGIA_Lim_2-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante</t>
+          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,41</t>
+          <t>0,22; 2,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,08</t>
+          <t>0,67; 3,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,88; 9,95</t>
+          <t>1,85; 9,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,3; 5,87</t>
+          <t>2,34; 6,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,46; 9,16</t>
+          <t>4,05; 8,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,77; 20,2</t>
+          <t>8,93; 20,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,47; 3,51</t>
+          <t>1,37; 3,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,65; 5,49</t>
+          <t>2,54; 5,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,92; 12,7</t>
+          <t>5,75; 12,16</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,38; 5,46</t>
+          <t>2,27; 5,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,81; 5,0</t>
+          <t>1,84; 5,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,66; 9,41</t>
+          <t>3,89; 9,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,08; 9,45</t>
+          <t>5,11; 9,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,49; 8,59</t>
+          <t>4,56; 8,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,29; 15,99</t>
+          <t>7,72; 16,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,12; 6,58</t>
+          <t>3,95; 6,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,49; 5,98</t>
+          <t>3,59; 6,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,79; 12,06</t>
+          <t>6,97; 11,9</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,9; 7,78</t>
+          <t>3,88; 7,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,99; 7,56</t>
+          <t>3,82; 7,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,53; 11,43</t>
+          <t>6,44; 11,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,13; 18,87</t>
+          <t>12,96; 18,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,97; 12,68</t>
+          <t>7,99; 12,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,88; 19,71</t>
+          <t>12,34; 19,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,08; 12,47</t>
+          <t>9,24; 12,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,49; 9,57</t>
+          <t>6,47; 9,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,77; 14,97</t>
+          <t>10,94; 15,12</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,43; 16,27</t>
+          <t>10,26; 16,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,32; 16,66</t>
+          <t>11,33; 17,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,86; 20,0</t>
+          <t>5,97; 20,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,36; 26,32</t>
+          <t>19,17; 26,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,57; 25,04</t>
+          <t>18,31; 24,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,46; 30,81</t>
+          <t>23,37; 30,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,78; 20,12</t>
+          <t>15,76; 20,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,79; 20,28</t>
+          <t>15,77; 20,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,61; 24,36</t>
+          <t>12,42; 24,46</t>
         </is>
       </c>
     </row>
@@ -1118,42 +1118,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>21,64; 30,44</t>
+          <t>21,98; 30,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19,58; 27,8</t>
+          <t>19,5; 27,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23,89; 30,81</t>
+          <t>24,26; 31,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40,43; 50,33</t>
+          <t>40,48; 50,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>34,15; 43,39</t>
+          <t>34,24; 43,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,13; 42,34</t>
+          <t>36,2; 42,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,44; 39,16</t>
+          <t>32,67; 39,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>27,98; 34,35</t>
+          <t>28,04; 34,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>44,49; 57,13</t>
+          <t>45,03; 57,05</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28,6; 38,94</t>
+          <t>28,8; 38,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25,04; 32,42</t>
+          <t>25,36; 32,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>56,43; 66,96</t>
+          <t>56,69; 67,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>47,83; 58,12</t>
+          <t>47,74; 58,07</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,81; 48,08</t>
+          <t>14,07; 48,03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>53,11; 60,85</t>
+          <t>52,8; 60,58</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>39,92; 47,75</t>
+          <t>40,33; 47,88</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16,59; 39,03</t>
+          <t>16,32; 39,0</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>59,88; 72,6</t>
+          <t>59,76; 72,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>44,7; 56,42</t>
+          <t>45,76; 56,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38,9; 48,14</t>
+          <t>39,04; 48,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>73,87; 82,74</t>
+          <t>74,18; 82,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>57,05; 68,21</t>
+          <t>56,89; 68,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,55; 71,62</t>
+          <t>65,34; 71,93</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,12; 77,48</t>
+          <t>70,15; 77,25</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>53,9; 62,5</t>
+          <t>54,1; 61,95</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>55,8; 61,57</t>
+          <t>55,96; 61,46</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>15,73; 18,34</t>
+          <t>15,72; 18,33</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13,72; 16,16</t>
+          <t>13,68; 16,16</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,6; 18,98</t>
+          <t>13,23; 19,06</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27,69; 30,8</t>
+          <t>27,84; 30,9</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>24,22; 27,3</t>
+          <t>24,29; 27,32</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,13; 32,18</t>
+          <t>23,51; 32,19</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,16; 24,31</t>
+          <t>22,25; 24,24</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>19,41; 21,46</t>
+          <t>19,38; 21,39</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>20,31; 25,31</t>
+          <t>20,14; 25,29</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante</t>
+          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>985; 10932</t>
+          <t>999; 9951</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2417; 12901</t>
+          <t>2815; 13413</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7527; 39809</t>
+          <t>7420; 38070</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9912; 25249</t>
+          <t>10074; 26440</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>17640; 36239</t>
+          <t>16046; 35451</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27478; 63260</t>
+          <t>27957; 62984</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13008; 31054</t>
+          <t>12097; 30268</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>21621; 44750</t>
+          <t>20743; 42875</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>42224; 90584</t>
+          <t>41023; 86752</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16386; 37543</t>
+          <t>15568; 36543</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10672; 29544</t>
+          <t>10861; 31056</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15483; 39858</t>
+          <t>16460; 39328</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30992; 57669</t>
+          <t>31179; 57310</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>25294; 48382</t>
+          <t>25706; 48438</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37325; 81891</t>
+          <t>39545; 82511</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>53419; 85411</t>
+          <t>51290; 84971</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>40280; 69045</t>
+          <t>41457; 72281</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>63549; 112829</t>
+          <t>65242; 111331</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>26604; 53069</t>
+          <t>26437; 52692</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>26675; 50559</t>
+          <t>25584; 50861</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>35023; 61325</t>
+          <t>34564; 61076</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>93352; 134151</t>
+          <t>92158; 133393</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>52718; 83859</t>
+          <t>52855; 83390</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>76262; 116659</t>
+          <t>73055; 116476</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>126437; 173612</t>
+          <t>128686; 175463</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>86284; 127277</t>
+          <t>86147; 125235</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>121504; 168957</t>
+          <t>123438; 170589</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>64128; 100020</t>
+          <t>63080; 100281</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>73150; 107612</t>
+          <t>73199; 111817</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>52041; 177585</t>
+          <t>52966; 178638</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>119293; 162160</t>
+          <t>118137; 161812</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>120517; 162506</t>
+          <t>118839; 160782</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>167224; 219673</t>
+          <t>166594; 218356</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>194174; 247645</t>
+          <t>193921; 251590</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>204461; 262685</t>
+          <t>204302; 262926</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>185812; 389991</t>
+          <t>198839; 391581</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>92913; 130705</t>
+          <t>94376; 129789</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>93556; 132861</t>
+          <t>93189; 133750</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>134070; 172938</t>
+          <t>136141; 175927</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>181066; 225396</t>
+          <t>181280; 225576</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>169655; 215604</t>
+          <t>170108; 213884</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>197931; 231971</t>
+          <t>198350; 233105</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>284567; 343545</t>
+          <t>286557; 344528</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>272777; 334804</t>
+          <t>273333; 335293</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>342346; 395814</t>
+          <t>342344; 395814</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>137820; 176977</t>
+          <t>139506; 176732</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>95605; 130196</t>
+          <t>96296; 129062</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>92204; 119345</t>
+          <t>93375; 120039</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>199756; 237037</t>
+          <t>200682; 237863</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>180685; 219556</t>
+          <t>180347; 219378</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>77961; 292506</t>
+          <t>85594; 292210</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>352552; 403940</t>
+          <t>350502; 402123</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>284280; 340016</t>
+          <t>287177; 340957</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>162040; 381159</t>
+          <t>159397; 380885</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>149601; 181396</t>
+          <t>149306; 181906</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>114879; 144990</t>
+          <t>117604; 146183</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>109979; 136131</t>
+          <t>110376; 136637</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>287320; 321830</t>
+          <t>288533; 322052</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>228287; 272937</t>
+          <t>227645; 273070</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>279126; 304972</t>
+          <t>278235; 306282</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>447978; 494957</t>
+          <t>448153; 493499</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>354210; 410734</t>
+          <t>355518; 407141</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>395421; 436265</t>
+          <t>396508; 435466</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>539147; 628616</t>
+          <t>538765; 628083</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>465684; 548403</t>
+          <t>464515; 548687</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>470623; 656562</t>
+          <t>457566; 659443</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>985463; 1095935</t>
+          <t>990630; 1099426</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>858554; 967781</t>
+          <t>860858; 968200</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>895754; 1194646</t>
+          <t>872848; 1194874</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1547932; 1698386</t>
+          <t>1554153; 1693328</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1346697; 1488780</t>
+          <t>1344647; 1484176</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1456828; 1814962</t>
+          <t>1444766; 1814112</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/POLIPATOLOGIA_Lim_2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/POLIPATOLOGIA_Lim_2-Edad-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,19</t>
+          <t>0,22; 2,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,2</t>
+          <t>0,59; 3,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 9,52</t>
+          <t>1,67; 8,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,34; 6,15</t>
+          <t>2,22; 6,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,05; 8,96</t>
+          <t>4,11; 8,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,93; 20,11</t>
+          <t>9,77; 20,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,42</t>
+          <t>1,37; 3,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,54; 5,26</t>
+          <t>2,69; 5,29</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,75; 12,16</t>
+          <t>6,32; 12,55</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,27; 5,32</t>
+          <t>2,34; 5,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,84; 5,26</t>
+          <t>1,8; 4,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,89; 9,29</t>
+          <t>3,66; 8,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,11; 9,39</t>
+          <t>4,98; 9,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,56; 8,6</t>
+          <t>4,6; 8,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,72; 16,11</t>
+          <t>10,2; 16,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,95; 6,55</t>
+          <t>4,17; 6,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,59; 6,26</t>
+          <t>3,55; 6,13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,97; 11,9</t>
+          <t>7,92; 12,14</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,46%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,88; 7,73</t>
+          <t>3,78; 7,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,82; 7,6</t>
+          <t>3,84; 7,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,44; 11,39</t>
+          <t>6,06; 11,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,96; 18,77</t>
+          <t>12,9; 18,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,99; 12,61</t>
+          <t>8,03; 12,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,34; 19,67</t>
+          <t>16,06; 21,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,24; 12,6</t>
+          <t>9,09; 12,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,47; 9,41</t>
+          <t>6,61; 9,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,94; 15,12</t>
+          <t>11,88; 15,45</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>23,72%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,26; 16,32</t>
+          <t>10,36; 15,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,33; 17,31</t>
+          <t>11,37; 16,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,97; 20,12</t>
+          <t>15,79; 22,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,17; 26,26</t>
+          <t>19,46; 26,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,31; 24,77</t>
+          <t>18,52; 24,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,37; 30,63</t>
+          <t>25,87; 31,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,76; 20,44</t>
+          <t>15,65; 20,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,77; 20,3</t>
+          <t>15,74; 20,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,42; 24,46</t>
+          <t>21,7; 25,64</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>32,99%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>21,98; 30,22</t>
+          <t>21,72; 30,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19,5; 27,99</t>
+          <t>19,59; 27,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24,26; 31,35</t>
+          <t>23,75; 30,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40,48; 50,37</t>
+          <t>40,73; 50,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>34,24; 43,05</t>
+          <t>34,03; 43,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,2; 42,54</t>
+          <t>36,05; 42,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,67; 39,27</t>
+          <t>32,91; 39,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>28,04; 34,4</t>
+          <t>27,83; 34,3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>30,87; 35,69</t>
+          <t>30,79; 35,29</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>37,82%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>45,03; 57,05</t>
+          <t>44,94; 56,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28,8; 38,6</t>
+          <t>28,43; 39,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25,36; 32,6</t>
+          <t>24,31; 31,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>56,69; 67,19</t>
+          <t>56,32; 67,45</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>47,74; 58,07</t>
+          <t>47,58; 58,07</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14,07; 48,03</t>
+          <t>43,52; 50,47</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>52,8; 60,58</t>
+          <t>53,14; 61,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>40,33; 47,88</t>
+          <t>40,16; 47,46</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16,32; 39,0</t>
+          <t>35,2; 40,31</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>58,59%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>59,76; 72,81</t>
+          <t>59,91; 72,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>45,76; 56,88</t>
+          <t>45,54; 56,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39,04; 48,32</t>
+          <t>38,59; 48,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>74,18; 82,79</t>
+          <t>73,77; 82,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>56,89; 68,24</t>
+          <t>58,0; 68,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,34; 71,93</t>
+          <t>64,94; 71,75</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,15; 77,25</t>
+          <t>69,76; 77,18</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>54,1; 61,95</t>
+          <t>54,16; 62,36</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>55,96; 61,46</t>
+          <t>55,9; 61,38</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>25,45%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>15,72; 18,33</t>
+          <t>15,65; 18,48</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13,68; 16,16</t>
+          <t>13,71; 16,23</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,23; 19,06</t>
+          <t>16,91; 19,58</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27,84; 30,9</t>
+          <t>27,74; 30,61</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>24,29; 27,32</t>
+          <t>24,22; 27,51</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,51; 32,19</t>
+          <t>31,23; 33,86</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,25; 24,24</t>
+          <t>22,12; 24,29</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>19,38; 21,39</t>
+          <t>19,49; 21,47</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>20,14; 25,29</t>
+          <t>24,43; 26,52</t>
         </is>
       </c>
     </row>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18464</t>
+          <t>17890</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42979</t>
+          <t>52649</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>61443</t>
+          <t>70538</t>
         </is>
       </c>
     </row>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>999; 9951</t>
+          <t>984; 9879</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2815; 13413</t>
+          <t>2478; 13259</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7420; 38070</t>
+          <t>6825; 36268</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10074; 26440</t>
+          <t>9554; 26186</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>16046; 35451</t>
+          <t>16279; 35011</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27957; 62984</t>
+          <t>35432; 75278</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12097; 30268</t>
+          <t>12151; 29709</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>20743; 42875</t>
+          <t>21928; 43121</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>41023; 86752</t>
+          <t>48674; 96691</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>25178</t>
+          <t>28212</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62879</t>
+          <t>67253</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>88056</t>
+          <t>95465</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15568; 36543</t>
+          <t>16061; 36333</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10861; 31056</t>
+          <t>10636; 28361</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16460; 39328</t>
+          <t>17445; 41687</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31179; 57310</t>
+          <t>30376; 56731</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>25706; 48438</t>
+          <t>25902; 49422</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>39545; 82511</t>
+          <t>51177; 84619</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>51290; 84971</t>
+          <t>54126; 86239</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>41457; 72281</t>
+          <t>40922; 70727</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>65242; 111331</t>
+          <t>77542; 118786</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47150</t>
+          <t>51557</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99236</t>
+          <t>115942</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>146386</t>
+          <t>167498</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>26437; 52692</t>
+          <t>25795; 52071</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>25584; 50861</t>
+          <t>25666; 50859</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34564; 61076</t>
+          <t>37649; 68395</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>92158; 133393</t>
+          <t>91709; 132148</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>52855; 83390</t>
+          <t>53077; 85453</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>73055; 116476</t>
+          <t>100066; 134420</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>128686; 175463</t>
+          <t>126619; 175605</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>86147; 125235</t>
+          <t>87909; 127709</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>123438; 170589</t>
+          <t>147837; 192150</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>122500</t>
+          <t>130316</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>197741</t>
+          <t>210665</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>320241</t>
+          <t>340981</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>63080; 100281</t>
+          <t>63699; 97694</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>73199; 111817</t>
+          <t>73476; 108499</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>52966; 178638</t>
+          <t>110651; 154673</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>118137; 161812</t>
+          <t>119941; 162733</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>118839; 160782</t>
+          <t>120200; 162106</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>166594; 218356</t>
+          <t>190666; 228789</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>193921; 251590</t>
+          <t>192594; 249371</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>204302; 262926</t>
+          <t>203875; 260370</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>198839; 391581</t>
+          <t>311915; 368613</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>153379</t>
+          <t>163648</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>215231</t>
+          <t>238289</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>368610</t>
+          <t>401936</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>94376; 129789</t>
+          <t>93282; 130611</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>93189; 133750</t>
+          <t>93604; 132912</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>136141; 175927</t>
+          <t>144744; 186272</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>181280; 225576</t>
+          <t>182399; 227061</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>170108; 213884</t>
+          <t>169070; 214803</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>198350; 233105</t>
+          <t>219495; 255993</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>286557; 344528</t>
+          <t>288720; 344565</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>273333; 335293</t>
+          <t>271317; 334332</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>342344; 395814</t>
+          <t>375115; 429954</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>105434</t>
+          <t>114318</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>188816</t>
+          <t>205740</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>294250</t>
+          <t>320059</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>139506; 176732</t>
+          <t>139209; 175707</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>96296; 129062</t>
+          <t>95045; 130628</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>93375; 120039</t>
+          <t>98944; 129552</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>200682; 237863</t>
+          <t>199377; 238754</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>180347; 219378</t>
+          <t>179726; 219350</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>85594; 292210</t>
+          <t>191141; 221635</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>350502; 402123</t>
+          <t>352763; 404969</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>287177; 340957</t>
+          <t>285960; 337994</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>159397; 380885</t>
+          <t>297855; 341103</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>122991</t>
+          <t>135051</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>292721</t>
+          <t>318877</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>415712</t>
+          <t>453929</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>149306; 181906</t>
+          <t>149693; 180139</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>117604; 146183</t>
+          <t>117048; 145469</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>110376; 136637</t>
+          <t>119700; 149097</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>288533; 322052</t>
+          <t>286948; 322006</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>227645; 273070</t>
+          <t>232101; 274862</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>278235; 306282</t>
+          <t>301710; 333380</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>448153; 493499</t>
+          <t>445658; 493028</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>355518; 407141</t>
+          <t>355903; 409800</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>396508; 435466</t>
+          <t>433110; 475538</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>595095</t>
+          <t>640992</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1099603</t>
+          <t>1209415</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1694698</t>
+          <t>1850407</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>538765; 628083</t>
+          <t>536420; 633209</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>464515; 548687</t>
+          <t>465378; 550763</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>457566; 659443</t>
+          <t>597395; 691624</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>990630; 1099426</t>
+          <t>987012; 1089080</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>860858; 968200</t>
+          <t>858479; 975038</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>872848; 1194874</t>
+          <t>1167141; 1265328</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1554153; 1693328</t>
+          <t>1545276; 1696504</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1344647; 1484176</t>
+          <t>1352608; 1490115</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1444766; 1814112</t>
+          <t>1775947; 1927855</t>
         </is>
       </c>
     </row>
